--- a/burocracy/diss_council.xlsx
+++ b/burocracy/diss_council.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PhD\disser\burocracy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE97ADA2-E718-46FF-AABA-15D7D669B934}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FA6EA4C-D3E0-420D-BD0E-D07E061A75C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{134430FC-25E2-4572-9815-FE2A91FBD179}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="64">
   <si>
     <t>№</t>
   </si>
@@ -184,6 +184,42 @@
   </si>
   <si>
     <t>Гошев Андрей Александрович</t>
+  </si>
+  <si>
+    <t>Витухновский</t>
+  </si>
+  <si>
+    <t>Григорьевич</t>
+  </si>
+  <si>
+    <t>Горшунов</t>
+  </si>
+  <si>
+    <t>Борис</t>
+  </si>
+  <si>
+    <t>Баранов Денис</t>
+  </si>
+  <si>
+    <t>Гольцман</t>
+  </si>
+  <si>
+    <t>Григорий</t>
+  </si>
+  <si>
+    <t>Наумович</t>
+  </si>
+  <si>
+    <t>МПГУ</t>
+  </si>
+  <si>
+    <t>Мещеринов Вячеслав Вячеславович</t>
+  </si>
+  <si>
+    <t>Написал рыбу?</t>
+  </si>
+  <si>
+    <t>Да</t>
   </si>
 </sst>
 </file>
@@ -200,12 +236,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -220,8 +268,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -536,10 +586,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3A0C460-2CFB-4414-A3CC-DFB3884CADAE}">
-  <dimension ref="B1:K11"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.88671875" bestFit="1" customWidth="1"/>
@@ -548,12 +599,15 @@
     <col min="9" max="9" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>62</v>
+      </c>
       <c r="K1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -582,73 +636,94 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="C3" t="s">
+    <row r="3" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" s="2">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="F3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="C4" t="s">
+    <row r="4" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" s="1">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="F4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="C5" t="s">
+    <row r="5" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="1">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="F5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <v>4</v>
+      </c>
       <c r="C6" t="s">
         <v>17</v>
       </c>
@@ -668,27 +743,36 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="C7" t="s">
+    <row r="7" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" s="1">
+        <v>5</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="F7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>6</v>
+      </c>
       <c r="C8" t="s">
         <v>35</v>
       </c>
@@ -708,7 +792,10 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>7</v>
+      </c>
       <c r="C9" t="s">
         <v>39</v>
       </c>
@@ -728,27 +815,33 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="C10" t="s">
+    <row r="10" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="2">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="F10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>9</v>
+      </c>
       <c r="C11" t="s">
         <v>47</v>
       </c>
@@ -768,7 +861,80 @@
         <v>51</v>
       </c>
     </row>
+    <row r="12" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" s="2">
+        <v>10</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>11</v>
+      </c>
+      <c r="C13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>12</v>
+      </c>
+      <c r="C14" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" t="s">
+        <v>59</v>
+      </c>
+      <c r="F14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" t="s">
+        <v>60</v>
+      </c>
+      <c r="H14" t="s">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/burocracy/diss_council.xlsx
+++ b/burocracy/diss_council.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PhD\disser\burocracy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FA6EA4C-D3E0-420D-BD0E-D07E061A75C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E27401A1-6EE4-43E1-938A-6F5C0D851376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{134430FC-25E2-4572-9815-FE2A91FBD179}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="71">
   <si>
     <t>№</t>
   </si>
@@ -132,9 +132,6 @@
     <t>председатель</t>
   </si>
   <si>
-    <t>точно будет</t>
-  </si>
-  <si>
     <t>Кузнецов</t>
   </si>
   <si>
@@ -216,17 +213,48 @@
     <t>Мещеринов Вячеслав Вячеславович</t>
   </si>
   <si>
-    <t>Написал рыбу?</t>
-  </si>
-  <si>
     <t>Да</t>
+  </si>
+  <si>
+    <t>Контакты</t>
+  </si>
+  <si>
+    <t>Написал рыбу анкеты?</t>
+  </si>
+  <si>
+    <t>astval@mail.ru
+astapenko.va@phystech.edu
+8(962)993-89-04</t>
+  </si>
+  <si>
+    <t>Председатель</t>
+  </si>
+  <si>
+    <t>8 (495) 702-93-17
+nailinogamov@gmail.com</t>
+  </si>
+  <si>
+    <t>vpkrainov@mail.ru
+krainov.vp@phystech.edu</t>
+  </si>
+  <si>
+    <t>kudryashovsi@lebedev.ru
+8(499) 132-60-83
+8(903) 185-02-46</t>
+  </si>
+  <si>
+    <t>8 903 504 9852
+murzina@mail.ru</t>
+  </si>
+  <si>
+    <t>vitukhnovsky@mail.ru +7(499) 132-63-64</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -235,8 +263,24 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -245,18 +289,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -264,16 +314,51 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -586,7 +671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3A0C460-2CFB-4414-A3CC-DFB3884CADAE}">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -596,345 +681,437 @@
     <col min="6" max="6" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="47.88671875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="27.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.44140625" customWidth="1"/>
+    <col min="10" max="10" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>63</v>
+      </c>
+      <c r="L1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="K1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="J2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2" s="4"/>
+    </row>
+    <row r="3" spans="1:13" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="5">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+    </row>
+    <row r="4" spans="1:13" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="5">
         <v>2</v>
       </c>
-      <c r="D2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="C4" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+    </row>
+    <row r="5" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="5">
         <v>3</v>
       </c>
-      <c r="F2" t="s">
+      <c r="C5" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+    </row>
+    <row r="6" spans="1:13" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" s="8">
+        <v>4</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M6" s="8"/>
+    </row>
+    <row r="7" spans="1:13" s="1" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" s="8">
+        <v>5</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+    </row>
+    <row r="8" spans="1:13" s="1" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" s="8">
+        <v>6</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+    </row>
+    <row r="9" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="12"/>
+      <c r="B9" s="12">
+        <v>7</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="12"/>
+    </row>
+    <row r="10" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="12"/>
+      <c r="B10" s="12">
+        <v>8</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="12"/>
+    </row>
+    <row r="11" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="12"/>
+      <c r="B11" s="12">
         <v>9</v>
       </c>
-      <c r="G2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H2" t="s">
-        <v>5</v>
-      </c>
-      <c r="I2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B3" s="2">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="C11" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I3" s="2" t="s">
+      <c r="H11" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="12"/>
+      <c r="M11" s="12"/>
+    </row>
+    <row r="12" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="12"/>
+      <c r="B12" s="12">
+        <v>10</v>
+      </c>
+      <c r="C12" s="12" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B4" s="1">
-        <v>2</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="1" t="s">
+      <c r="D12" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="12"/>
+    </row>
+    <row r="13" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="12"/>
+      <c r="B13" s="12">
         <v>11</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="C13" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="12"/>
+    </row>
+    <row r="14" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="12"/>
+      <c r="B14" s="12">
         <v>12</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5" s="1">
-        <v>3</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B7" s="1">
-        <v>5</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B8">
-        <v>6</v>
-      </c>
-      <c r="C8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" t="s">
-        <v>37</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" t="s">
-        <v>38</v>
-      </c>
-      <c r="H8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B9">
-        <v>7</v>
-      </c>
-      <c r="C9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" t="s">
-        <v>41</v>
-      </c>
-      <c r="F9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" t="s">
-        <v>42</v>
-      </c>
-      <c r="H9" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="2">
-        <v>8</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="C14" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B11">
-        <v>9</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="D14" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E14" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F14" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="F11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="H14" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="H11" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B12" s="2">
-        <v>10</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B13">
-        <v>11</v>
-      </c>
-      <c r="C13" t="s">
-        <v>54</v>
-      </c>
-      <c r="D13" t="s">
-        <v>55</v>
-      </c>
-      <c r="E13" t="s">
-        <v>37</v>
-      </c>
-      <c r="F13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H13" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B14">
-        <v>12</v>
-      </c>
-      <c r="C14" t="s">
-        <v>57</v>
-      </c>
-      <c r="D14" t="s">
-        <v>58</v>
-      </c>
-      <c r="E14" t="s">
-        <v>59</v>
-      </c>
-      <c r="F14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" t="s">
-        <v>60</v>
-      </c>
-      <c r="H14" t="s">
-        <v>61</v>
-      </c>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="12"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I3" r:id="rId1" display="astval@mail.ru_x000a_8(962)993-89-04" xr:uid="{55B80AD8-BB63-400C-82C8-D1A2D95E682B}"/>
+    <hyperlink ref="I4" r:id="rId2" display="mailto:vpkrainov@mail.ru" xr:uid="{B85A9B67-6B35-4E7E-B7BA-C6FE4984F297}"/>
+    <hyperlink ref="I6" r:id="rId3" xr:uid="{1B5ADA78-8CBD-43E8-A167-CE865E1C4D3A}"/>
+    <hyperlink ref="I5" r:id="rId4" display="mailto:vitukhnovsky@mail.ru" xr:uid="{A2FFBEB8-9E0D-469A-A860-49F874F54EBF}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
 </worksheet>
 </file>
--- a/burocracy/diss_council.xlsx
+++ b/burocracy/diss_council.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PhD\disser\burocracy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E27401A1-6EE4-43E1-938A-6F5C0D851376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EDB140E-C129-4D5B-9495-0B49C3FB16D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{134430FC-25E2-4572-9815-FE2A91FBD179}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="74">
   <si>
     <t>№</t>
   </si>
@@ -248,6 +248,15 @@
   </si>
   <si>
     <t>vitukhnovsky@mail.ru +7(499) 132-63-64</t>
+  </si>
+  <si>
+    <t>Согласился?</t>
+  </si>
+  <si>
+    <t>Отправил анкету?</t>
+  </si>
+  <si>
+    <t>Забрал оригинал заявы+анкеты?</t>
   </si>
 </sst>
 </file>
@@ -671,445 +680,498 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3A0C460-2CFB-4414-A3CC-DFB3884CADAE}">
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="47.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="27.44140625" customWidth="1"/>
-    <col min="10" max="10" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="14" customWidth="1"/>
+    <col min="6" max="6" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="47.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="27.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.44140625" customWidth="1"/>
+    <col min="13" max="13" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>63</v>
       </c>
-      <c r="L1" t="s">
+      <c r="B1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="4"/>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="K2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="L2" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="M2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4" t="s">
+      <c r="N2" s="4"/>
+      <c r="O2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="4"/>
-    </row>
-    <row r="3" spans="1:13" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="P2" s="4"/>
+    </row>
+    <row r="3" spans="1:16" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5">
         <v>1</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="F3" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="G3" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="5" t="s">
+      <c r="I3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="K3" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="L3" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="M3" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-    </row>
-    <row r="4" spans="1:13" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+    </row>
+    <row r="4" spans="1:16" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5">
         <v>2</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="F4" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="G4" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="H4" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="5" t="s">
+      <c r="I4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="K4" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="L4" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
       <c r="M4" s="5"/>
-    </row>
-    <row r="5" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+    </row>
+    <row r="5" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5">
         <v>3</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="G5" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="H5" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="5" t="s">
+      <c r="I5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="K5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="L5" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
       <c r="M5" s="5"/>
-    </row>
-    <row r="6" spans="1:13" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+    </row>
+    <row r="6" spans="1:16" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8">
         <v>4</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="F6" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="G6" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="H6" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="8" t="s">
+      <c r="I6" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J6" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="K6" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="L6" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8" t="s">
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="M6" s="8"/>
-    </row>
-    <row r="7" spans="1:13" s="1" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="P6" s="8"/>
+    </row>
+    <row r="7" spans="1:16" s="1" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8">
         <v>5</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="F7" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="G7" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="H7" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="8" t="s">
+      <c r="I7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="K7" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="L7" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
       <c r="M7" s="8"/>
-    </row>
-    <row r="8" spans="1:13" s="1" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+    </row>
+    <row r="8" spans="1:16" s="1" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8">
         <v>6</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="F8" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="G8" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="H8" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="8" t="s">
+      <c r="I8" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J8" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="K8" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="I8" s="11" t="s">
+      <c r="L8" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
       <c r="M8" s="8"/>
-    </row>
-    <row r="9" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+    </row>
+    <row r="9" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12"/>
-      <c r="B9" s="12">
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12">
         <v>7</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="F9" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="G9" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="H9" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" s="12" t="s">
+      <c r="I9" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="J9" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="K9" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="12"/>
       <c r="L9" s="12"/>
       <c r="M9" s="12"/>
-    </row>
-    <row r="10" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="N9" s="12"/>
+      <c r="O9" s="12"/>
+      <c r="P9" s="12"/>
+    </row>
+    <row r="10" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
-      <c r="B10" s="12">
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12">
         <v>8</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="F10" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="G10" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="H10" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="F10" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="12" t="s">
+      <c r="I10" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="J10" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="K10" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
       <c r="L10" s="12"/>
       <c r="M10" s="12"/>
-    </row>
-    <row r="11" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="N10" s="12"/>
+      <c r="O10" s="12"/>
+      <c r="P10" s="12"/>
+    </row>
+    <row r="11" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="12"/>
-      <c r="B11" s="12">
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12">
         <v>9</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="F11" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="G11" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="H11" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F11" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="12" t="s">
+      <c r="I11" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="J11" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H11" s="12" t="s">
+      <c r="K11" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
       <c r="L11" s="12"/>
       <c r="M11" s="12"/>
-    </row>
-    <row r="12" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="N11" s="12"/>
+      <c r="O11" s="12"/>
+      <c r="P11" s="12"/>
+    </row>
+    <row r="12" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
-      <c r="B12" s="12">
-        <v>10</v>
-      </c>
-      <c r="C12" s="12" t="s">
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12">
+        <v>10</v>
+      </c>
+      <c r="F12" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="G12" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="H12" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F12" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="12" t="s">
+      <c r="I12" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="J12" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="H12" s="12" t="s">
+      <c r="K12" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
       <c r="L12" s="12"/>
       <c r="M12" s="12"/>
-    </row>
-    <row r="13" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="N12" s="12"/>
+      <c r="O12" s="12"/>
+      <c r="P12" s="12"/>
+    </row>
+    <row r="13" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
-      <c r="B13" s="12">
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12">
         <v>11</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="F13" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="G13" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="H13" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="F13" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="12" t="s">
+      <c r="I13" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="J13" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="H13" s="12" t="s">
+      <c r="K13" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
       <c r="L13" s="12"/>
       <c r="M13" s="12"/>
-    </row>
-    <row r="14" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="N13" s="12"/>
+      <c r="O13" s="12"/>
+      <c r="P13" s="12"/>
+    </row>
+    <row r="14" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="12"/>
-      <c r="B14" s="12">
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12">
         <v>12</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="F14" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="G14" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="H14" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" s="12" t="s">
+      <c r="I14" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="J14" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="H14" s="12" t="s">
+      <c r="K14" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
       <c r="L14" s="12"/>
       <c r="M14" s="12"/>
+      <c r="N14" s="12"/>
+      <c r="O14" s="12"/>
+      <c r="P14" s="12"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="I3" r:id="rId1" display="astval@mail.ru_x000a_8(962)993-89-04" xr:uid="{55B80AD8-BB63-400C-82C8-D1A2D95E682B}"/>
-    <hyperlink ref="I4" r:id="rId2" display="mailto:vpkrainov@mail.ru" xr:uid="{B85A9B67-6B35-4E7E-B7BA-C6FE4984F297}"/>
-    <hyperlink ref="I6" r:id="rId3" xr:uid="{1B5ADA78-8CBD-43E8-A167-CE865E1C4D3A}"/>
-    <hyperlink ref="I5" r:id="rId4" display="mailto:vitukhnovsky@mail.ru" xr:uid="{A2FFBEB8-9E0D-469A-A860-49F874F54EBF}"/>
+    <hyperlink ref="L3" r:id="rId1" display="astval@mail.ru_x000a_8(962)993-89-04" xr:uid="{55B80AD8-BB63-400C-82C8-D1A2D95E682B}"/>
+    <hyperlink ref="L4" r:id="rId2" display="mailto:vpkrainov@mail.ru" xr:uid="{B85A9B67-6B35-4E7E-B7BA-C6FE4984F297}"/>
+    <hyperlink ref="L6" r:id="rId3" xr:uid="{1B5ADA78-8CBD-43E8-A167-CE865E1C4D3A}"/>
+    <hyperlink ref="L5" r:id="rId4" display="mailto:vitukhnovsky@mail.ru" xr:uid="{A2FFBEB8-9E0D-469A-A860-49F874F54EBF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>

--- a/burocracy/diss_council.xlsx
+++ b/burocracy/diss_council.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PhD\disser\burocracy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EDB140E-C129-4D5B-9495-0B49C3FB16D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{026B7C22-F28D-4F22-8027-98211BFE8706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{134430FC-25E2-4572-9815-FE2A91FBD179}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="80">
   <si>
     <t>№</t>
   </si>
@@ -257,13 +257,31 @@
   </si>
   <si>
     <t>Забрал оригинал заявы+анкеты?</t>
+  </si>
+  <si>
+    <t>пнул 10 августа</t>
+  </si>
+  <si>
+    <t>ответила 10 августа просит ждать</t>
+  </si>
+  <si>
+    <t>отказ</t>
+  </si>
+  <si>
+    <t>Нет</t>
+  </si>
+  <si>
+    <t>Написал 11 августа</t>
+  </si>
+  <si>
+    <t>apkuznetsov@mephi.ru</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -287,6 +305,23 @@
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -343,7 +378,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -355,9 +390,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -365,6 +397,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -680,11 +718,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3A0C460-2CFB-4414-A3CC-DFB3884CADAE}">
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="14" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="14" customWidth="1"/>
     <col min="6" max="6" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.33203125" bestFit="1" customWidth="1"/>
@@ -832,7 +871,9 @@
       <c r="A5" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B5" s="5"/>
+      <c r="B5" s="5" t="s">
+        <v>74</v>
+      </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5">
@@ -864,49 +905,51 @@
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
     </row>
-    <row r="6" spans="1:16" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8">
-        <v>4</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="I6" s="8" t="s">
+    <row r="6" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11">
         <v>10</v>
       </c>
-      <c r="J6" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="L6" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="P6" s="8"/>
+      <c r="F6" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="11"/>
+      <c r="P6" s="11"/>
     </row>
     <row r="7" spans="1:16" s="1" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B7" s="8"/>
+      <c r="B7" s="8" t="s">
+        <v>75</v>
+      </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8">
@@ -930,7 +973,7 @@
       <c r="K7" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="L7" s="10" t="s">
+      <c r="L7" s="9" t="s">
         <v>69</v>
       </c>
       <c r="M7" s="8"/>
@@ -942,7 +985,9 @@
       <c r="A8" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B8" s="8"/>
+      <c r="B8" s="8" t="s">
+        <v>61</v>
+      </c>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
       <c r="E8" s="8">
@@ -966,7 +1011,7 @@
       <c r="K8" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="L8" s="11" t="s">
+      <c r="L8" s="10" t="s">
         <v>66</v>
       </c>
       <c r="M8" s="8"/>
@@ -975,205 +1020,214 @@
       <c r="P8" s="8"/>
     </row>
     <row r="9" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="12"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12">
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11">
         <v>7</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="G9" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="H9" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="I9" s="12" t="s">
+      <c r="I9" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="J9" s="12" t="s">
+      <c r="J9" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K9" s="12" t="s">
+      <c r="K9" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="L9" s="12"/>
-      <c r="M9" s="12"/>
-      <c r="N9" s="12"/>
-      <c r="O9" s="12"/>
-      <c r="P9" s="12"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="11"/>
+      <c r="P9" s="11"/>
     </row>
     <row r="10" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="12"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12">
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11">
         <v>8</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G10" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="H10" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="I10" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="J10" s="12" t="s">
+      <c r="J10" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="K10" s="12" t="s">
+      <c r="K10" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="L10" s="12"/>
-      <c r="M10" s="12"/>
-      <c r="N10" s="12"/>
-      <c r="O10" s="12"/>
-      <c r="P10" s="12"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="11"/>
+      <c r="O10" s="11"/>
+      <c r="P10" s="11"/>
     </row>
     <row r="11" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11">
         <v>9</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="G11" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H11" s="12" t="s">
+      <c r="H11" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="I11" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="J11" s="12" t="s">
+      <c r="J11" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K11" s="12" t="s">
+      <c r="K11" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="L11" s="12"/>
-      <c r="M11" s="12"/>
-      <c r="N11" s="12"/>
-      <c r="O11" s="12"/>
-      <c r="P11" s="12"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="11"/>
+      <c r="P11" s="11"/>
     </row>
     <row r="12" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11">
+        <v>11</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="I12" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="G12" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="H12" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="I12" s="12" t="s">
+      <c r="J12" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="11"/>
+      <c r="O12" s="11"/>
+      <c r="P12" s="11"/>
+    </row>
+    <row r="13" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11">
+        <v>12</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="I13" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="J12" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="K12" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="L12" s="12"/>
-      <c r="M12" s="12"/>
-      <c r="N12" s="12"/>
-      <c r="O12" s="12"/>
-      <c r="P12" s="12"/>
-    </row>
-    <row r="13" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="12"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12">
+      <c r="J13" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="11"/>
+      <c r="P13" s="11"/>
+    </row>
+    <row r="15" spans="1:16" s="14" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12">
+        <v>4</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="J15" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="F13" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="G13" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="H13" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="I13" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="J13" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="K13" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="L13" s="12"/>
-      <c r="M13" s="12"/>
-      <c r="N13" s="12"/>
-      <c r="O13" s="12"/>
-      <c r="P13" s="12"/>
-    </row>
-    <row r="14" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12">
+      <c r="K15" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="F14" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="G14" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="H14" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="I14" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="J14" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="K14" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="L14" s="12"/>
-      <c r="M14" s="12"/>
-      <c r="N14" s="12"/>
-      <c r="O14" s="12"/>
-      <c r="P14" s="12"/>
+      <c r="L15" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="M15" s="12"/>
+      <c r="N15" s="12"/>
+      <c r="O15" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="P15" s="12"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="L3" r:id="rId1" display="astval@mail.ru_x000a_8(962)993-89-04" xr:uid="{55B80AD8-BB63-400C-82C8-D1A2D95E682B}"/>
     <hyperlink ref="L4" r:id="rId2" display="mailto:vpkrainov@mail.ru" xr:uid="{B85A9B67-6B35-4E7E-B7BA-C6FE4984F297}"/>
-    <hyperlink ref="L6" r:id="rId3" xr:uid="{1B5ADA78-8CBD-43E8-A167-CE865E1C4D3A}"/>
+    <hyperlink ref="L15" r:id="rId3" xr:uid="{1B5ADA78-8CBD-43E8-A167-CE865E1C4D3A}"/>
     <hyperlink ref="L5" r:id="rId4" display="mailto:vitukhnovsky@mail.ru" xr:uid="{A2FFBEB8-9E0D-469A-A860-49F874F54EBF}"/>
+    <hyperlink ref="L6" r:id="rId5" xr:uid="{4321ECF0-D9B7-4C17-8D2B-E91123E62F46}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
 </worksheet>
 </file>
--- a/burocracy/diss_council.xlsx
+++ b/burocracy/diss_council.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PhD\disser\burocracy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{026B7C22-F28D-4F22-8027-98211BFE8706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EF23ECF-B879-4622-91AA-6C9596245E4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{134430FC-25E2-4572-9815-FE2A91FBD179}"/>
   </bookViews>
@@ -28,10 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="80">
-  <si>
-    <t>№</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="91">
   <si>
     <t>Имя</t>
   </si>
@@ -262,9 +259,6 @@
     <t>пнул 10 августа</t>
   </si>
   <si>
-    <t>ответила 10 августа просит ждать</t>
-  </si>
-  <si>
     <t>отказ</t>
   </si>
   <si>
@@ -275,6 +269,45 @@
   </si>
   <si>
     <t>apkuznetsov@mephi.ru</t>
+  </si>
+  <si>
+    <t>Кукушкин</t>
+  </si>
+  <si>
+    <t>Борисович</t>
+  </si>
+  <si>
+    <t>Курчатовский институт</t>
+  </si>
+  <si>
+    <t>Бергалиев Тимур</t>
+  </si>
+  <si>
+    <t>Kukushkin_AB@ncki.ru</t>
+  </si>
+  <si>
+    <t>написал 17 августа</t>
+  </si>
+  <si>
+    <t>14 августа согласна но может не быть в мск на защите</t>
+  </si>
+  <si>
+    <t>Андреев</t>
+  </si>
+  <si>
+    <t>Степан</t>
+  </si>
+  <si>
+    <t>Николаевич</t>
+  </si>
+  <si>
+    <t>andreev_stepan@mail.ru4</t>
+  </si>
+  <si>
+    <t>merzlikin_a@mail.ru, a.m.merzlikin@gmail.com</t>
+  </si>
+  <si>
+    <t>НАПИШИИИИ</t>
   </si>
 </sst>
 </file>
@@ -378,31 +411,50 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -718,516 +770,554 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3A0C460-2CFB-4414-A3CC-DFB3884CADAE}">
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="14" customWidth="1"/>
-    <col min="6" max="6" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="47.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="27.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="27.44140625" customWidth="1"/>
-    <col min="13" max="13" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="14" style="5" customWidth="1"/>
+    <col min="5" max="5" width="13.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.88671875" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="47.88671875" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.44140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="27.44140625" style="5" customWidth="1"/>
+    <col min="12" max="12" width="11.77734375" style="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="O2" s="6"/>
+    </row>
+    <row r="3" spans="1:15" s="8" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="L3" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+    </row>
+    <row r="4" spans="1:15" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+    </row>
+    <row r="5" spans="1:15" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
+    </row>
+    <row r="6" spans="1:15" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="O1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="I2" s="4" t="s">
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="H6" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="K2" s="4" t="s">
+      <c r="I6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+    </row>
+    <row r="7" spans="1:15" s="11" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+    </row>
+    <row r="9" spans="1:15" s="11" customFormat="1" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+    </row>
+    <row r="10" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="7"/>
+    </row>
+    <row r="11" spans="1:15" s="11" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+    </row>
+    <row r="12" spans="1:15" s="10" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="9"/>
+    </row>
+    <row r="13" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="9"/>
+    </row>
+    <row r="14" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
+    </row>
+    <row r="16" spans="1:15" s="13" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4" t="s">
+      <c r="F16" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="J16" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="L16" s="12"/>
+      <c r="M16" s="12"/>
+      <c r="N16" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="P2" s="4"/>
-    </row>
-    <row r="3" spans="1:16" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5">
-        <v>1</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-    </row>
-    <row r="4" spans="1:16" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5">
-        <v>2</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-    </row>
-    <row r="5" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="O16" s="12"/>
+    </row>
+    <row r="17" spans="1:15" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="12"/>
+      <c r="B17" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5">
-        <v>3</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-    </row>
-    <row r="6" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="B6" s="11" t="s">
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11">
-        <v>10</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="K6" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="L6" s="15" t="s">
+      <c r="F17" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="G17" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
-      <c r="O6" s="11"/>
-      <c r="P6" s="11"/>
-    </row>
-    <row r="7" spans="1:16" s="1" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8">
-        <v>5</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="L7" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
-    </row>
-    <row r="8" spans="1:16" s="1" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8">
-        <v>6</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="L8" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8"/>
-    </row>
-    <row r="9" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11">
-        <v>7</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="J9" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="K9" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="11"/>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-    </row>
-    <row r="10" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11">
-        <v>8</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="K10" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="11"/>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-    </row>
-    <row r="11" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11">
+      <c r="H17" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="J11" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="K11" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-    </row>
-    <row r="12" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11">
-        <v>11</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="H12" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="J12" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="K12" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="11"/>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-    </row>
-    <row r="13" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11">
-        <v>12</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="J13" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="K13" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-    </row>
-    <row r="15" spans="1:16" s="14" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12">
-        <v>4</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="G15" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="H15" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="I15" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="J15" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="K15" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="L15" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="M15" s="12"/>
-      <c r="N15" s="12"/>
-      <c r="O15" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="P15" s="12"/>
+      <c r="I17" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="J17" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="L17" s="12"/>
+      <c r="M17" s="12"/>
+      <c r="N17" s="12"/>
+      <c r="O17" s="12"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="L3" r:id="rId1" display="astval@mail.ru_x000a_8(962)993-89-04" xr:uid="{55B80AD8-BB63-400C-82C8-D1A2D95E682B}"/>
-    <hyperlink ref="L4" r:id="rId2" display="mailto:vpkrainov@mail.ru" xr:uid="{B85A9B67-6B35-4E7E-B7BA-C6FE4984F297}"/>
-    <hyperlink ref="L15" r:id="rId3" xr:uid="{1B5ADA78-8CBD-43E8-A167-CE865E1C4D3A}"/>
-    <hyperlink ref="L5" r:id="rId4" display="mailto:vitukhnovsky@mail.ru" xr:uid="{A2FFBEB8-9E0D-469A-A860-49F874F54EBF}"/>
-    <hyperlink ref="L6" r:id="rId5" xr:uid="{4321ECF0-D9B7-4C17-8D2B-E91123E62F46}"/>
+    <hyperlink ref="K3" r:id="rId1" display="astval@mail.ru_x000a_8(962)993-89-04" xr:uid="{55B80AD8-BB63-400C-82C8-D1A2D95E682B}"/>
+    <hyperlink ref="K4" r:id="rId2" display="mailto:vpkrainov@mail.ru" xr:uid="{B85A9B67-6B35-4E7E-B7BA-C6FE4984F297}"/>
+    <hyperlink ref="K16" r:id="rId3" xr:uid="{1B5ADA78-8CBD-43E8-A167-CE865E1C4D3A}"/>
+    <hyperlink ref="K6" r:id="rId4" display="mailto:vitukhnovsky@mail.ru" xr:uid="{A2FFBEB8-9E0D-469A-A860-49F874F54EBF}"/>
+    <hyperlink ref="K8" r:id="rId5" xr:uid="{4321ECF0-D9B7-4C17-8D2B-E91123E62F46}"/>
+    <hyperlink ref="K17" r:id="rId6" xr:uid="{1DF5DB8B-DE1C-4CE8-8E1F-37F1833ED1FE}"/>
+    <hyperlink ref="K5" r:id="rId7" xr:uid="{797371FE-0D11-42CE-8332-E27D72E9D370}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId8"/>
 </worksheet>
 </file>
--- a/burocracy/diss_council.xlsx
+++ b/burocracy/diss_council.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PhD\disser\burocracy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EF23ECF-B879-4622-91AA-6C9596245E4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D122B2-BC82-4CB2-9961-74C79E4A0905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{134430FC-25E2-4572-9815-FE2A91FBD179}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="91">
   <si>
     <t>Имя</t>
   </si>
@@ -307,7 +307,7 @@
     <t>merzlikin_a@mail.ru, a.m.merzlikin@gmail.com</t>
   </si>
   <si>
-    <t>НАПИШИИИИ</t>
+    <t>Написал 19 августа</t>
   </si>
 </sst>
 </file>
@@ -883,7 +883,9 @@
       <c r="B4" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C4" s="7"/>
+      <c r="C4" s="7" t="s">
+        <v>60</v>
+      </c>
       <c r="D4" s="7"/>
       <c r="E4" s="7" t="s">
         <v>42</v>
@@ -913,12 +915,14 @@
     </row>
     <row r="5" spans="1:15" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="7"/>
+      <c r="C5" s="7" t="s">
+        <v>60</v>
+      </c>
       <c r="D5" s="7"/>
       <c r="E5" s="7" t="s">
         <v>85</v>
@@ -988,7 +992,9 @@
       <c r="B7" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C7" s="2"/>
+      <c r="C7" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
         <v>21</v>
@@ -1150,34 +1156,36 @@
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
     </row>
-    <row r="12" spans="1:15" s="10" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9" t="s">
+    <row r="12" spans="1:15" s="11" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I12" s="9" t="s">
+      <c r="I12" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="J12" s="9" t="s">
+      <c r="J12" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
     </row>
     <row r="13" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9"/>

--- a/burocracy/diss_council.xlsx
+++ b/burocracy/diss_council.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PhD\disser\burocracy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D122B2-BC82-4CB2-9961-74C79E4A0905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEDBF539-A84F-4E57-B77E-042444C7B5BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{134430FC-25E2-4572-9815-FE2A91FBD179}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="97">
   <si>
     <t>Имя</t>
   </si>
@@ -308,6 +308,24 @@
   </si>
   <si>
     <t>Написал 19 августа</t>
+  </si>
+  <si>
+    <t>Макаров</t>
+  </si>
+  <si>
+    <t>Дмитрий</t>
+  </si>
+  <si>
+    <t>Северный институт</t>
+  </si>
+  <si>
+    <t>d.makarov@narfu.ru</t>
+  </si>
+  <si>
+    <t>только онлайн</t>
+  </si>
+  <si>
+    <t>может не хватить публикаций</t>
   </si>
 </sst>
 </file>
@@ -770,7 +788,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3A0C460-2CFB-4414-A3CC-DFB3884CADAE}">
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" style="5" bestFit="1" customWidth="1"/>
@@ -913,7 +931,7 @@
       <c r="N4" s="7"/>
       <c r="O4" s="7"/>
     </row>
-    <row r="5" spans="1:15" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" s="8" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>60</v>
       </c>
@@ -945,47 +963,51 @@
       <c r="K5" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="L5" s="7"/>
+      <c r="L5" s="7" t="s">
+        <v>96</v>
+      </c>
       <c r="M5" s="7"/>
       <c r="N5" s="7"/>
       <c r="O5" s="7"/>
     </row>
-    <row r="6" spans="1:15" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-    </row>
-    <row r="7" spans="1:15" s="11" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" s="11" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+    </row>
+    <row r="7" spans="1:15" s="11" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>60</v>
       </c>
@@ -997,224 +1019,232 @@
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>22</v>
+        <v>92</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>23</v>
+        <v>87</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="L7" s="2"/>
+        <v>94</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>95</v>
+      </c>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
     </row>
-    <row r="8" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:15" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+    </row>
+    <row r="9" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B9" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K8" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-    </row>
-    <row r="9" spans="1:15" s="11" customFormat="1" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>84</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>68</v>
+        <v>20</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>77</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
     </row>
-    <row r="10" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7" t="s">
+    <row r="10" spans="1:15" s="11" customFormat="1" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+    </row>
+    <row r="11" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7" t="s">
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F11" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G11" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="H10" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="I10" s="7" t="s">
+      <c r="H11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I11" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="J11" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
-      <c r="O10" s="7"/>
-    </row>
-    <row r="11" spans="1:15" s="11" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
     </row>
     <row r="12" spans="1:15" s="11" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="2" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="K12" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>89</v>
+      </c>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
     </row>
-    <row r="13" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
+    <row r="13" spans="1:15" s="11" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
     </row>
     <row r="14" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9"/>
@@ -1222,22 +1252,22 @@
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>9</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="K14" s="9"/>
       <c r="L14" s="9"/>
@@ -1245,85 +1275,114 @@
       <c r="N14" s="9"/>
       <c r="O14" s="9"/>
     </row>
-    <row r="16" spans="1:15" s="13" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="G16" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="H16" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="I16" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="J16" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="L16" s="12"/>
-      <c r="M16" s="12"/>
-      <c r="N16" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="O16" s="12"/>
-    </row>
-    <row r="17" spans="1:15" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="12"/>
+    <row r="15" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="9"/>
+    </row>
+    <row r="17" spans="1:15" s="13" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A17" s="12" t="s">
+        <v>60</v>
+      </c>
       <c r="B17" s="12" t="s">
         <v>74</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
       <c r="E17" s="12" t="s">
-        <v>78</v>
+        <v>5</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>79</v>
+        <v>7</v>
       </c>
       <c r="H17" s="12" t="s">
         <v>9</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="12"/>
-      <c r="N17" s="12"/>
+      <c r="N17" s="12" t="s">
+        <v>26</v>
+      </c>
       <c r="O17" s="12"/>
+    </row>
+    <row r="18" spans="1:15" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="12"/>
+      <c r="B18" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="I18" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="J18" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
+      <c r="O18" s="12"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="K3" r:id="rId1" display="astval@mail.ru_x000a_8(962)993-89-04" xr:uid="{55B80AD8-BB63-400C-82C8-D1A2D95E682B}"/>
     <hyperlink ref="K4" r:id="rId2" display="mailto:vpkrainov@mail.ru" xr:uid="{B85A9B67-6B35-4E7E-B7BA-C6FE4984F297}"/>
-    <hyperlink ref="K16" r:id="rId3" xr:uid="{1B5ADA78-8CBD-43E8-A167-CE865E1C4D3A}"/>
-    <hyperlink ref="K6" r:id="rId4" display="mailto:vitukhnovsky@mail.ru" xr:uid="{A2FFBEB8-9E0D-469A-A860-49F874F54EBF}"/>
-    <hyperlink ref="K8" r:id="rId5" xr:uid="{4321ECF0-D9B7-4C17-8D2B-E91123E62F46}"/>
-    <hyperlink ref="K17" r:id="rId6" xr:uid="{1DF5DB8B-DE1C-4CE8-8E1F-37F1833ED1FE}"/>
-    <hyperlink ref="K5" r:id="rId7" xr:uid="{797371FE-0D11-42CE-8332-E27D72E9D370}"/>
+    <hyperlink ref="K17" r:id="rId3" xr:uid="{1B5ADA78-8CBD-43E8-A167-CE865E1C4D3A}"/>
+    <hyperlink ref="K9" r:id="rId4" xr:uid="{4321ECF0-D9B7-4C17-8D2B-E91123E62F46}"/>
+    <hyperlink ref="K18" r:id="rId5" xr:uid="{1DF5DB8B-DE1C-4CE8-8E1F-37F1833ED1FE}"/>
+    <hyperlink ref="K5" r:id="rId6" xr:uid="{797371FE-0D11-42CE-8332-E27D72E9D370}"/>
+    <hyperlink ref="K8" r:id="rId7" display="mailto:vitukhnovsky@mail.ru" xr:uid="{6DD08A79-9682-486A-8C22-FF1C2B887D81}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId8"/>

--- a/burocracy/diss_council.xlsx
+++ b/burocracy/diss_council.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PhD\disser\burocracy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEDBF539-A84F-4E57-B77E-042444C7B5BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41146D4A-0A7D-4285-994A-4AACCA3EA8FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{134430FC-25E2-4572-9815-FE2A91FBD179}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="98">
   <si>
     <t>Имя</t>
   </si>
@@ -326,6 +326,9 @@
   </si>
   <si>
     <t>может не хватить публикаций</t>
+  </si>
+  <si>
+    <t>24 августа: ИНА в больнице на Минской, лучше тогда в пятницу</t>
   </si>
 </sst>
 </file>
@@ -970,7 +973,7 @@
       <c r="N5" s="7"/>
       <c r="O5" s="7"/>
     </row>
-    <row r="6" spans="1:15" s="11" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" s="11" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>60</v>
       </c>
@@ -980,7 +983,9 @@
       <c r="C6" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="D6" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>21</v>
       </c>

--- a/burocracy/diss_council.xlsx
+++ b/burocracy/diss_council.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PhD\disser\burocracy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41146D4A-0A7D-4285-994A-4AACCA3EA8FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF2BB395-3ED4-4BFD-B9C4-B8A652E107E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{134430FC-25E2-4572-9815-FE2A91FBD179}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="105">
   <si>
     <t>Имя</t>
   </si>
@@ -265,9 +265,6 @@
     <t>Нет</t>
   </si>
   <si>
-    <t>Написал 11 августа</t>
-  </si>
-  <si>
     <t>apkuznetsov@mephi.ru</t>
   </si>
   <si>
@@ -289,9 +286,6 @@
     <t>написал 17 августа</t>
   </si>
   <si>
-    <t>14 августа согласна но может не быть в мск на защите</t>
-  </si>
-  <si>
     <t>Андреев</t>
   </si>
   <si>
@@ -329,13 +323,42 @@
   </si>
   <si>
     <t>24 августа: ИНА в больнице на Минской, лучше тогда в пятницу</t>
+  </si>
+  <si>
+    <t>Написал 25 августа</t>
+  </si>
+  <si>
+    <t>Чернега</t>
+  </si>
+  <si>
+    <t>Николай</t>
+  </si>
+  <si>
+    <t>Владимирович</t>
+  </si>
+  <si>
+    <t>ФИАН</t>
+  </si>
+  <si>
+    <t>Маресев Александр</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> tchera@lebedev.ru
+Email: ntcherniega@gmail.com
+Телефон: +7(499)132-65-51</t>
+  </si>
+  <si>
+    <t>пнул 27 августа</t>
+  </si>
+  <si>
+    <t>пнул 27 августа по поводу встречи</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -372,6 +395,23 @@
       <u/>
       <sz val="11"/>
       <color theme="0" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1" tint="0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1" tint="0.499984740745262"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
@@ -432,7 +472,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -474,6 +514,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -791,7 +840,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3A0C460-2CFB-4414-A3CC-DFB3884CADAE}">
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" style="5" bestFit="1" customWidth="1"/>
@@ -946,13 +995,13 @@
       </c>
       <c r="D5" s="7"/>
       <c r="E5" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="G5" s="7" t="s">
         <v>85</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>87</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>9</v>
@@ -964,10 +1013,10 @@
         <v>59</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="M5" s="7"/>
       <c r="N5" s="7"/>
@@ -984,7 +1033,7 @@
         <v>60</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>21</v>
@@ -1024,74 +1073,74 @@
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="J7" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="K7" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I7" s="2" t="s">
+      <c r="L7" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
     </row>
-    <row r="8" spans="1:15" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
+    <row r="8" spans="1:15" s="11" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
     </row>
     <row r="9" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>75</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -1114,7 +1163,7 @@
         <v>20</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
@@ -1126,7 +1175,7 @@
         <v>60</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -1159,7 +1208,7 @@
     <row r="11" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7"/>
       <c r="B11" s="7" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -1190,7 +1239,7 @@
     <row r="12" spans="1:15" s="11" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -1213,7 +1262,7 @@
         <v>41</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
@@ -1223,7 +1272,7 @@
     <row r="13" spans="1:15" s="11" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
       <c r="B13" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -1309,87 +1358,123 @@
       <c r="N15" s="9"/>
       <c r="O15" s="9"/>
     </row>
-    <row r="17" spans="1:15" s="13" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A17" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="G17" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="H17" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="I17" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="J17" s="12" t="s">
+    <row r="17" spans="1:15" s="17" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="H17" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="I17" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="J17" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="K17" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="L17" s="12"/>
-      <c r="M17" s="12"/>
-      <c r="N17" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="O17" s="12"/>
-    </row>
-    <row r="18" spans="1:15" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="12"/>
+      <c r="K17" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="15"/>
+      <c r="O17" s="15"/>
+    </row>
+    <row r="18" spans="1:15" s="13" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A18" s="12" t="s">
+        <v>60</v>
+      </c>
       <c r="B18" s="12" t="s">
         <v>74</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
       <c r="E18" s="12" t="s">
-        <v>78</v>
+        <v>5</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>79</v>
+        <v>7</v>
       </c>
       <c r="H18" s="12" t="s">
         <v>9</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12"/>
-      <c r="N18" s="12"/>
+      <c r="N18" s="12" t="s">
+        <v>26</v>
+      </c>
       <c r="O18" s="12"/>
+    </row>
+    <row r="19" spans="1:15" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="12"/>
+      <c r="B19" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="H19" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="I19" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="L19" s="12"/>
+      <c r="M19" s="12"/>
+      <c r="N19" s="12"/>
+      <c r="O19" s="12"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="K3" r:id="rId1" display="astval@mail.ru_x000a_8(962)993-89-04" xr:uid="{55B80AD8-BB63-400C-82C8-D1A2D95E682B}"/>
     <hyperlink ref="K4" r:id="rId2" display="mailto:vpkrainov@mail.ru" xr:uid="{B85A9B67-6B35-4E7E-B7BA-C6FE4984F297}"/>
-    <hyperlink ref="K17" r:id="rId3" xr:uid="{1B5ADA78-8CBD-43E8-A167-CE865E1C4D3A}"/>
-    <hyperlink ref="K9" r:id="rId4" xr:uid="{4321ECF0-D9B7-4C17-8D2B-E91123E62F46}"/>
-    <hyperlink ref="K18" r:id="rId5" xr:uid="{1DF5DB8B-DE1C-4CE8-8E1F-37F1833ED1FE}"/>
-    <hyperlink ref="K5" r:id="rId6" xr:uid="{797371FE-0D11-42CE-8332-E27D72E9D370}"/>
-    <hyperlink ref="K8" r:id="rId7" display="mailto:vitukhnovsky@mail.ru" xr:uid="{6DD08A79-9682-486A-8C22-FF1C2B887D81}"/>
+    <hyperlink ref="K18" r:id="rId3" xr:uid="{1B5ADA78-8CBD-43E8-A167-CE865E1C4D3A}"/>
+    <hyperlink ref="K19" r:id="rId4" xr:uid="{1DF5DB8B-DE1C-4CE8-8E1F-37F1833ED1FE}"/>
+    <hyperlink ref="K5" r:id="rId5" xr:uid="{797371FE-0D11-42CE-8332-E27D72E9D370}"/>
+    <hyperlink ref="K8" r:id="rId6" display="apkuznetsov@mephi.ru" xr:uid="{90BE1B57-92FA-4760-8287-57E3C95F92BD}"/>
+    <hyperlink ref="K9" r:id="rId7" xr:uid="{4321ECF0-D9B7-4C17-8D2B-E91123E62F46}"/>
+    <hyperlink ref="K17" r:id="rId8" display="mailto:vitukhnovsky@mail.ru" xr:uid="{ED38466C-E47C-4C68-B243-6E8D2F2C6F98}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId8"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId9"/>
 </worksheet>
 </file>
--- a/burocracy/diss_council.xlsx
+++ b/burocracy/diss_council.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PhD\disser\burocracy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF2BB395-3ED4-4BFD-B9C4-B8A652E107E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE00DF60-C386-4ED2-92DA-33C828692C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{134430FC-25E2-4572-9815-FE2A91FBD179}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="106">
   <si>
     <t>Имя</t>
   </si>
@@ -100,9 +100,6 @@
   </si>
   <si>
     <t>Алимович</t>
-  </si>
-  <si>
-    <t>6 человек</t>
   </si>
   <si>
     <t>от 2 до 4 МФТИ</t>
@@ -352,6 +349,12 @@
   </si>
   <si>
     <t>пнул 27 августа по поводу встречи</t>
+  </si>
+  <si>
+    <t>Брантов</t>
+  </si>
+  <si>
+    <t>в пути из Архангельска</t>
   </si>
 </sst>
 </file>
@@ -859,73 +862,104 @@
   <sheetData>
     <row r="1" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" s="8" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="O2" s="6"/>
-    </row>
-    <row r="3" spans="1:15" s="8" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="L2" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+    </row>
+    <row r="3" spans="1:15" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
+        <v>59</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>59</v>
+      </c>
       <c r="E3" s="7" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="H3" s="7" t="s">
         <v>9</v>
@@ -934,37 +968,37 @@
         <v>19</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>64</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="L3" s="7"/>
       <c r="M3" s="7"/>
       <c r="N3" s="7"/>
       <c r="O3" s="7"/>
     </row>
-    <row r="4" spans="1:15" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" s="8" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D4" s="7"/>
+        <v>59</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>59</v>
+      </c>
       <c r="E4" s="7" t="s">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>9</v>
@@ -973,162 +1007,164 @@
         <v>19</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="L4" s="7"/>
+        <v>85</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>93</v>
+      </c>
       <c r="M4" s="7"/>
       <c r="N4" s="7"/>
       <c r="O4" s="7"/>
     </row>
-    <row r="5" spans="1:15" s="8" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="F5" s="7" t="s">
+    <row r="5" spans="1:15" s="11" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+    </row>
+    <row r="6" spans="1:15" s="11" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G5" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-    </row>
-    <row r="6" spans="1:15" s="11" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="H6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="L6" s="2"/>
+        <v>91</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
     </row>
-    <row r="7" spans="1:15" s="11" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" s="11" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D7" s="2"/>
+        <v>59</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>59</v>
+      </c>
       <c r="E7" s="2" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>93</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="K7" s="3"/>
+      <c r="L7" s="2"/>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
     </row>
     <row r="8" spans="1:15" s="11" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="H8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I8" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="K8" s="14" t="s">
         <v>101</v>
-      </c>
-      <c r="K8" s="14" t="s">
-        <v>102</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
@@ -1137,33 +1173,33 @@
     </row>
     <row r="9" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="H9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>20</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
@@ -1172,10 +1208,10 @@
     </row>
     <row r="10" spans="1:15" s="11" customFormat="1" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -1198,7 +1234,7 @@
         <v>11</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
@@ -1208,18 +1244,18 @@
     <row r="11" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7"/>
       <c r="B11" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
       <c r="E11" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F11" s="7" t="s">
-        <v>53</v>
-      </c>
       <c r="G11" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>9</v>
@@ -1228,7 +1264,7 @@
         <v>19</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K11" s="7"/>
       <c r="L11" s="7"/>
@@ -1239,30 +1275,30 @@
     <row r="12" spans="1:15" s="11" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="G12" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="H12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="H12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I12" s="2" t="s">
+      <c r="J12" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="J12" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="K12" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
@@ -1272,27 +1308,27 @@
     <row r="13" spans="1:15" s="11" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
       <c r="B13" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="G13" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="H13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="H13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I13" s="2" t="s">
+      <c r="J13" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
@@ -1335,22 +1371,22 @@
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="F15" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="G15" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="H15" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="I15" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="I15" s="9" t="s">
+      <c r="J15" s="9" t="s">
         <v>48</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>49</v>
       </c>
       <c r="K15" s="9"/>
       <c r="L15" s="9"/>
@@ -1360,21 +1396,21 @@
     </row>
     <row r="17" spans="1:15" s="17" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C17" s="15"/>
       <c r="D17" s="15"/>
       <c r="E17" s="15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F17" s="15" t="s">
         <v>17</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H17" s="15" t="s">
         <v>9</v>
@@ -1386,7 +1422,7 @@
         <v>11</v>
       </c>
       <c r="K17" s="16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L17" s="15"/>
       <c r="M17" s="15"/>
@@ -1395,10 +1431,10 @@
     </row>
     <row r="18" spans="1:15" s="13" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -1421,42 +1457,42 @@
         <v>11</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="12"/>
       <c r="N18" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O18" s="12"/>
     </row>
     <row r="19" spans="1:15" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="12"/>
       <c r="B19" s="12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
       <c r="E19" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="G19" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="F19" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="G19" s="12" t="s">
+      <c r="H19" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="I19" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="H19" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="I19" s="12" t="s">
+      <c r="J19" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="J19" s="12" t="s">
+      <c r="K19" s="4" t="s">
         <v>80</v>
-      </c>
-      <c r="K19" s="4" t="s">
-        <v>81</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="12"/>
@@ -1465,11 +1501,11 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="K3" r:id="rId1" display="astval@mail.ru_x000a_8(962)993-89-04" xr:uid="{55B80AD8-BB63-400C-82C8-D1A2D95E682B}"/>
-    <hyperlink ref="K4" r:id="rId2" display="mailto:vpkrainov@mail.ru" xr:uid="{B85A9B67-6B35-4E7E-B7BA-C6FE4984F297}"/>
+    <hyperlink ref="K2" r:id="rId1" display="astval@mail.ru_x000a_8(962)993-89-04" xr:uid="{55B80AD8-BB63-400C-82C8-D1A2D95E682B}"/>
+    <hyperlink ref="K3" r:id="rId2" display="mailto:vpkrainov@mail.ru" xr:uid="{B85A9B67-6B35-4E7E-B7BA-C6FE4984F297}"/>
     <hyperlink ref="K18" r:id="rId3" xr:uid="{1B5ADA78-8CBD-43E8-A167-CE865E1C4D3A}"/>
     <hyperlink ref="K19" r:id="rId4" xr:uid="{1DF5DB8B-DE1C-4CE8-8E1F-37F1833ED1FE}"/>
-    <hyperlink ref="K5" r:id="rId5" xr:uid="{797371FE-0D11-42CE-8332-E27D72E9D370}"/>
+    <hyperlink ref="K4" r:id="rId5" xr:uid="{797371FE-0D11-42CE-8332-E27D72E9D370}"/>
     <hyperlink ref="K8" r:id="rId6" display="apkuznetsov@mephi.ru" xr:uid="{90BE1B57-92FA-4760-8287-57E3C95F92BD}"/>
     <hyperlink ref="K9" r:id="rId7" xr:uid="{4321ECF0-D9B7-4C17-8D2B-E91123E62F46}"/>
     <hyperlink ref="K17" r:id="rId8" display="mailto:vitukhnovsky@mail.ru" xr:uid="{ED38466C-E47C-4C68-B243-6E8D2F2C6F98}"/>

--- a/burocracy/diss_council.xlsx
+++ b/burocracy/diss_council.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PhD\disser\burocracy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE00DF60-C386-4ED2-92DA-33C828692C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CDAEC47-D98F-4695-A940-7F001677097A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{134430FC-25E2-4572-9815-FE2A91FBD179}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="112">
   <si>
     <t>Имя</t>
   </si>
@@ -52,9 +52,6 @@
   </si>
   <si>
     <t>Иванович</t>
-  </si>
-  <si>
-    <t>уч степень</t>
   </si>
   <si>
     <t>дфмн</t>
@@ -319,9 +316,6 @@
     <t>может не хватить публикаций</t>
   </si>
   <si>
-    <t>24 августа: ИНА в больнице на Минской, лучше тогда в пятницу</t>
-  </si>
-  <si>
     <t>Написал 25 августа</t>
   </si>
   <si>
@@ -355,6 +349,31 @@
   </si>
   <si>
     <t>в пути из Архангельска</t>
+  </si>
+  <si>
+    <t>когда удобно</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Мне удобнее по понедельникам и средам (весь день) или в любой другой день в первой половине дня. </t>
+  </si>
+  <si>
+    <t>Все дни мне удобны, так как у меня лекции в МФТИ по субботам.</t>
+  </si>
+  <si>
+    <t>Дату выберите сами, мне тяжело сейчас спланировать в декабре когда у меня будет свободное время, постараюсь под дату защиты спланировать время</t>
+  </si>
+  <si>
+    <t>НАПИШИ ЕМУ</t>
+  </si>
+  <si>
+    <t>в принципе такая возможность есть, с 3 ноября по 3 декабря с.г. у меня планируется командировка.</t>
+  </si>
+  <si>
+    <t>89168069632
+brantovav@lebedev.ru</t>
+  </si>
+  <si>
+    <t>написал 03/09/26</t>
   </si>
 </sst>
 </file>
@@ -843,18 +862,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3A0C460-2CFB-4414-A3CC-DFB3884CADAE}">
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="14" style="5" customWidth="1"/>
+    <col min="1" max="1" width="14" style="5" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" style="5" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="14" style="5" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="14" style="5" customWidth="1"/>
     <col min="5" max="5" width="13.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.33203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.88671875" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="47.88671875" style="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="27.44140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="45.44140625" style="5" customWidth="1"/>
+    <col min="9" max="9" width="18.21875" style="5" customWidth="1"/>
+    <col min="10" max="10" width="22.33203125" style="5" customWidth="1"/>
     <col min="11" max="11" width="27.44140625" style="5" customWidth="1"/>
     <col min="12" max="12" width="11.77734375" style="5" bestFit="1" customWidth="1"/>
     <col min="13" max="16384" width="8.88671875" style="5"/>
@@ -862,16 +882,16 @@
   <sheetData>
     <row r="1" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>70</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>71</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>1</v>
@@ -883,7 +903,7 @@
         <v>2</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>8</v>
+        <v>104</v>
       </c>
       <c r="I1" s="6" t="s">
         <v>3</v>
@@ -892,48 +912,48 @@
         <v>4</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M1" s="6"/>
       <c r="N1" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:15" s="8" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C2" s="7"/>
       <c r="D2" s="7"/>
       <c r="E2" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="G2" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="H2" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="H2" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>31</v>
-      </c>
       <c r="K2" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="L2" s="7" t="s">
         <v>62</v>
-      </c>
-      <c r="L2" s="7" t="s">
-        <v>63</v>
       </c>
       <c r="M2" s="7"/>
       <c r="N2" s="7"/>
@@ -941,37 +961,37 @@
     </row>
     <row r="3" spans="1:15" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E3" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="G3" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="G3" s="7" t="s">
-        <v>43</v>
-      </c>
       <c r="H3" s="7" t="s">
-        <v>9</v>
+        <v>106</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
@@ -980,535 +1000,524 @@
     </row>
     <row r="4" spans="1:15" s="8" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E4" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="G4" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="H4" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="H4" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>85</v>
-      </c>
       <c r="L4" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M4" s="7"/>
       <c r="N4" s="7"/>
       <c r="O4" s="7"/>
     </row>
-    <row r="5" spans="1:15" s="11" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" s="11" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="H5" s="2" t="s">
-        <v>9</v>
+        <v>108</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
     </row>
-    <row r="6" spans="1:15" s="11" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" s="11" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I6" s="2" t="s">
+      <c r="J6" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K6" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="J6" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="K6" s="3" t="s">
+      <c r="L6" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
     </row>
-    <row r="7" spans="1:15" s="11" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" s="11" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G7" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="K7" s="3"/>
+      <c r="K7" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
     </row>
-    <row r="8" spans="1:15" s="11" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B8" s="2" t="s">
+    <row r="8" spans="1:15" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="9" spans="1:15" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:15" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:15" s="11" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2" t="s">
+      <c r="G11" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="H11" s="2"/>
+      <c r="I11" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="J11" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I8" s="2" t="s">
+      <c r="K11" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+    </row>
+    <row r="12" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="K8" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-    </row>
-    <row r="9" spans="1:15" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K9" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
-    </row>
-    <row r="10" spans="1:15" s="11" customFormat="1" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-    </row>
-    <row r="11" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="7"/>
-      <c r="O11" s="7"/>
-    </row>
-    <row r="12" spans="1:15" s="11" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2" t="s">
-        <v>81</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>86</v>
+        <v>19</v>
+      </c>
+      <c r="K12" s="14" t="s">
+        <v>74</v>
       </c>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
     </row>
-    <row r="13" spans="1:15" s="11" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="2"/>
+    <row r="13" spans="1:15" s="11" customFormat="1" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="B13" s="2" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="K13" s="2"/>
+        <v>10</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
     </row>
-    <row r="14" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9" t="s">
+    <row r="14" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7"/>
+    </row>
+    <row r="15" spans="1:15" s="11" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+    </row>
+    <row r="16" spans="1:15" s="11" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+    </row>
+    <row r="17" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="G17" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="H17" s="9"/>
+      <c r="I17" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="J17" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="9"/>
+    </row>
+    <row r="18" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="J18" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="9"/>
+    </row>
+    <row r="20" spans="1:15" s="17" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="H20" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="J20" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L20" s="15"/>
+      <c r="M20" s="15"/>
+      <c r="N20" s="15"/>
+      <c r="O20" s="15"/>
+    </row>
+    <row r="21" spans="1:15" s="13" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A21" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G21" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="I14" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
-    </row>
-    <row r="15" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
-      <c r="N15" s="9"/>
-      <c r="O15" s="9"/>
-    </row>
-    <row r="17" spans="1:15" s="17" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="B17" s="15" t="s">
+      <c r="J21" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="L21" s="12"/>
+      <c r="M21" s="12"/>
+      <c r="N21" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="O21" s="12"/>
+    </row>
+    <row r="22" spans="1:15" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="12"/>
+      <c r="B22" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="F17" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="G17" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="H17" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="I17" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="J17" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="K17" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="L17" s="15"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="15"/>
-      <c r="O17" s="15"/>
-    </row>
-    <row r="18" spans="1:15" s="13" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A18" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="G18" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="H18" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="I18" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="J18" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="L18" s="12"/>
-      <c r="M18" s="12"/>
-      <c r="N18" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="O18" s="12"/>
-    </row>
-    <row r="19" spans="1:15" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12" t="s">
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G22" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="F19" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="G19" s="12" t="s">
+      <c r="H22" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="H19" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="I19" s="12" t="s">
+      <c r="J22" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="J19" s="12" t="s">
+      <c r="K22" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="K19" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="L19" s="12"/>
-      <c r="M19" s="12"/>
-      <c r="N19" s="12"/>
-      <c r="O19" s="12"/>
+      <c r="L22" s="12"/>
+      <c r="M22" s="12"/>
+      <c r="N22" s="12"/>
+      <c r="O22" s="12"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="K2" r:id="rId1" display="astval@mail.ru_x000a_8(962)993-89-04" xr:uid="{55B80AD8-BB63-400C-82C8-D1A2D95E682B}"/>
     <hyperlink ref="K3" r:id="rId2" display="mailto:vpkrainov@mail.ru" xr:uid="{B85A9B67-6B35-4E7E-B7BA-C6FE4984F297}"/>
-    <hyperlink ref="K18" r:id="rId3" xr:uid="{1B5ADA78-8CBD-43E8-A167-CE865E1C4D3A}"/>
-    <hyperlink ref="K19" r:id="rId4" xr:uid="{1DF5DB8B-DE1C-4CE8-8E1F-37F1833ED1FE}"/>
+    <hyperlink ref="K21" r:id="rId3" xr:uid="{1B5ADA78-8CBD-43E8-A167-CE865E1C4D3A}"/>
+    <hyperlink ref="K22" r:id="rId4" xr:uid="{1DF5DB8B-DE1C-4CE8-8E1F-37F1833ED1FE}"/>
     <hyperlink ref="K4" r:id="rId5" xr:uid="{797371FE-0D11-42CE-8332-E27D72E9D370}"/>
-    <hyperlink ref="K8" r:id="rId6" display="apkuznetsov@mephi.ru" xr:uid="{90BE1B57-92FA-4760-8287-57E3C95F92BD}"/>
-    <hyperlink ref="K9" r:id="rId7" xr:uid="{4321ECF0-D9B7-4C17-8D2B-E91123E62F46}"/>
-    <hyperlink ref="K17" r:id="rId8" display="mailto:vitukhnovsky@mail.ru" xr:uid="{ED38466C-E47C-4C68-B243-6E8D2F2C6F98}"/>
+    <hyperlink ref="K11" r:id="rId6" display="apkuznetsov@mephi.ru" xr:uid="{90BE1B57-92FA-4760-8287-57E3C95F92BD}"/>
+    <hyperlink ref="K12" r:id="rId7" xr:uid="{4321ECF0-D9B7-4C17-8D2B-E91123E62F46}"/>
+    <hyperlink ref="K20" r:id="rId8" display="mailto:vitukhnovsky@mail.ru" xr:uid="{ED38466C-E47C-4C68-B243-6E8D2F2C6F98}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId9"/>
